--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398B35F1-A632-487B-848E-297A655FFC3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2E2F7A9-C698-46C7-8A7D-268D82AAF6B4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76C42D1-E96A-47C6-989D-F5125DC91168}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501DAEAD-33EB-4173-B50D-B1277B1AE73E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD4EF802-0431-447F-A7A2-2F7585B10514}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBE4D7-F1FF-4CA5-B7A5-5853EA9F02FA}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/RE0508-14082024-152338.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2E2F7A9-C698-46C7-8A7D-268D82AAF6B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{398B35F1-A632-487B-848E-297A655FFC3B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501DAEAD-33EB-4173-B50D-B1277B1AE73E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76C42D1-E96A-47C6-989D-F5125DC91168}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBE4D7-F1FF-4CA5-B7A5-5853EA9F02FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD4EF802-0431-447F-A7A2-2F7585B10514}"/>
 </file>